--- a/docs/REVISION-CAMPO.xlsx
+++ b/docs/REVISION-CAMPO.xlsx
@@ -150,7 +150,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
